--- a/public/templates/members-template.xlsx
+++ b/public/templates/members-template.xlsx
@@ -31,7 +31,7 @@
     <t>기수(선택)</t>
   </si>
   <si>
-    <t>상태(선택, 기본값 재학)</t>
+    <t>상태(선택, 기본값 과정 진행중)</t>
   </si>
 </sst>
 </file>
